--- a/División/UOri_División.xlsx
+++ b/División/UOri_División.xlsx
@@ -428,16 +428,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="2">
-        <v>46.90947659382043</v>
+        <v>46.90947659382044</v>
       </c>
       <c r="C2" s="2">
-        <v>116.0833909375528</v>
+        <v>116.0741668374778</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>54.45411110116439</v>
+        <v>54.44978412409876</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -465,13 +465,13 @@
         <v>15.40948540940612</v>
       </c>
       <c r="C4" s="2">
-        <v>114.1559714932756</v>
+        <v>114.1559714932755</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E4" s="2">
-        <v>17.5908477712221</v>
+        <v>17.59084777122211</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -479,7 +479,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="2">
-        <v>19.06039588067198</v>
+        <v>19.06039588067199</v>
       </c>
       <c r="C5" s="2">
         <v>114.243722332753</v>
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="E5" s="2">
-        <v>21.7753057454384</v>
+        <v>21.77530574543841</v>
       </c>
     </row>
   </sheetData>
